--- a/business_surveys/015_ride_hailing_company_evaluation_survey--business_surveys.xlsx
+++ b/business_surveys/015_ride_hailing_company_evaluation_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>san_jose</t>
+          <t>seattle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Seattle</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>seattle</t>
+          <t>indianapolis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Indianapolis</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>indianapolis</t>
+          <t>boston</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Boston</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>city_choices</t>
+          <t>service_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1178,29 +1178,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>service_choices</t>
+          <t>safety_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>most_of_the_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Most of the time</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>most_of_the_time</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Most of the time</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>seldom</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Seldom</t>
         </is>
       </c>
     </row>
@@ -1263,29 +1263,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>seldom</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seldom</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>safety_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1297,27 +1297,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>communication_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
